--- a/tasks/finalpool/terminal-wc-pw-pricing-excel-word-gcal/groundtruth_workspace/Competitive_Pricing_Report.xlsx
+++ b/tasks/finalpool/terminal-wc-pw-pricing-excel-word-gcal/groundtruth_workspace/Competitive_Pricing_Report.xlsx
@@ -426,7 +426,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Regular_Price</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
